--- a/business2.xlsx
+++ b/business2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\seigo\Desktop\授業\2025後期授業\ビジネス実践演習\11月12日\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{900B161B-0B62-48DE-84CA-1C24AD0C5717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{152325E8-5FA5-46ED-AB84-1ECB8B26AD67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="事例1" sheetId="1" r:id="rId1"/>
@@ -704,19 +704,19 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C2">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D2">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E2">
         <v>58</v>
       </c>
       <c r="F2">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.15">
@@ -724,19 +724,19 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C3">
         <v>85</v>
       </c>
       <c r="D3">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E3">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F3">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.15">
@@ -744,19 +744,19 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C4">
+        <v>70</v>
+      </c>
+      <c r="D4">
         <v>68</v>
       </c>
-      <c r="D4">
-        <v>65</v>
-      </c>
       <c r="E4">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F4">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.15">
@@ -764,19 +764,19 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C5">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D5">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E5">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F5">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.15">
@@ -784,19 +784,19 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C6">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D6">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E6">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F6">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.15">
@@ -804,19 +804,19 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C7">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D7">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E7">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F7">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.15">
@@ -824,19 +824,19 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C8">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D8">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E8">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F8">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.15">
@@ -844,13 +844,13 @@
         <v>13</v>
       </c>
       <c r="B9">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C9">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D9">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E9">
         <v>85</v>
@@ -870,13 +870,13 @@
         <v>93</v>
       </c>
       <c r="D10">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E10">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F10">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.15">
@@ -884,19 +884,19 @@
         <v>15</v>
       </c>
       <c r="B11">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C11">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D11">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E11">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F11">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.15">
@@ -904,19 +904,19 @@
         <v>16</v>
       </c>
       <c r="B12">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C12">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D12">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="E12">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F12">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.15">
@@ -924,19 +924,19 @@
         <v>17</v>
       </c>
       <c r="B13">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C13">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D13">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="E13">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F13">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.15">
@@ -944,13 +944,13 @@
         <v>18</v>
       </c>
       <c r="B14">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C14">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D14">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E14">
         <v>83</v>
@@ -964,19 +964,19 @@
         <v>19</v>
       </c>
       <c r="B15">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C15">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D15">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E15">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F15">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.15">
@@ -984,13 +984,13 @@
         <v>20</v>
       </c>
       <c r="B16">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C16">
+        <v>73</v>
+      </c>
+      <c r="D16">
         <v>71</v>
-      </c>
-      <c r="D16">
-        <v>68</v>
       </c>
       <c r="E16">
         <v>81</v>
@@ -1004,13 +1004,13 @@
         <v>21</v>
       </c>
       <c r="B17">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C17">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D17">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="E17">
         <v>70</v>
@@ -1024,19 +1024,19 @@
         <v>22</v>
       </c>
       <c r="B18">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C18">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D18">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E18">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F18">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.15">
@@ -1044,19 +1044,19 @@
         <v>23</v>
       </c>
       <c r="B19">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C19">
+        <v>88</v>
+      </c>
+      <c r="D19">
         <v>85</v>
       </c>
-      <c r="D19">
-        <v>80</v>
-      </c>
       <c r="E19">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F19">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.15">
@@ -1064,19 +1064,19 @@
         <v>24</v>
       </c>
       <c r="B20">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C20">
+        <v>67</v>
+      </c>
+      <c r="D20">
         <v>65</v>
       </c>
-      <c r="D20">
-        <v>63</v>
-      </c>
       <c r="E20">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F20">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.15">
@@ -1084,19 +1084,19 @@
         <v>25</v>
       </c>
       <c r="B21">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C21">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D21">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E21">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F21">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
